--- a/Assets/SimpleSolitaire/Data/Words.xlsx
+++ b/Assets/SimpleSolitaire/Data/Words.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -57,6 +57,183 @@
   </si>
   <si>
     <t>ICON资源ID</t>
+  </si>
+  <si>
+    <t>披萨</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>炸薯条</t>
+  </si>
+  <si>
+    <t>热狗</t>
+  </si>
+  <si>
+    <t>炸鸡</t>
+  </si>
+  <si>
+    <t>苹果派</t>
+  </si>
+  <si>
+    <t>芝士通心粉</t>
+  </si>
+  <si>
+    <t>美国烤肉</t>
+  </si>
+  <si>
+    <t>封面</t>
+  </si>
+  <si>
+    <t>纸张</t>
+  </si>
+  <si>
+    <t>页</t>
+  </si>
+  <si>
+    <t>目录</t>
+  </si>
+  <si>
+    <t>扉页</t>
+  </si>
+  <si>
+    <t>版权页</t>
+  </si>
+  <si>
+    <t>书脊</t>
+  </si>
+  <si>
+    <t>封底</t>
+  </si>
+  <si>
+    <t>年</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>周</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>动作片</t>
+  </si>
+  <si>
+    <t>喜剧片</t>
+  </si>
+  <si>
+    <t>科幻片</t>
+  </si>
+  <si>
+    <t>西部片</t>
+  </si>
+  <si>
+    <t>剧情片</t>
+  </si>
+  <si>
+    <t>恐怖片</t>
+  </si>
+  <si>
+    <t>爱情片</t>
+  </si>
+  <si>
+    <t>动画片</t>
+  </si>
+  <si>
+    <t>面饼</t>
+  </si>
+  <si>
+    <t>番茄酱</t>
+  </si>
+  <si>
+    <t>肉饼</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+  </si>
+  <si>
+    <t>酸黄瓜</t>
+  </si>
+  <si>
+    <t>洋葱</t>
+  </si>
+  <si>
+    <t>生菜</t>
+  </si>
+  <si>
+    <t>芝士</t>
+  </si>
+  <si>
+    <t>浣熊</t>
+  </si>
+  <si>
+    <t>郊狼</t>
+  </si>
+  <si>
+    <t>马</t>
+  </si>
+  <si>
+    <t>松树</t>
+  </si>
+  <si>
+    <t>棕熊</t>
+  </si>
+  <si>
+    <t>白头海雕</t>
+  </si>
+  <si>
+    <t>鹿</t>
+  </si>
+  <si>
+    <t>美洲野牛</t>
+  </si>
+  <si>
+    <t>欧洲</t>
+  </si>
+  <si>
+    <t>亚洲</t>
+  </si>
+  <si>
+    <t>非洲</t>
+  </si>
+  <si>
+    <t>北美洲</t>
+  </si>
+  <si>
+    <t>南美洲</t>
+  </si>
+  <si>
+    <t>大洋洲</t>
+  </si>
+  <si>
+    <t>南极洲</t>
+  </si>
+  <si>
+    <t>缎面</t>
+  </si>
+  <si>
+    <t>毛毡布</t>
+  </si>
+  <si>
+    <t>麻布</t>
+  </si>
+  <si>
+    <t>丝绸</t>
+  </si>
+  <si>
+    <t>法兰绒</t>
+  </si>
+  <si>
+    <t>天鹅绒</t>
+  </si>
+  <si>
+    <t>棉布</t>
+  </si>
+  <si>
+    <t>亚麻布</t>
   </si>
 </sst>
 </file>
@@ -69,9 +246,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -416,12 +600,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -542,141 +741,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,8 +1409,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.23076923076923" style="1"/>
     <col min="2" max="2" width="15.5384615384615" style="1" customWidth="1"/>
@@ -1248,6 +1453,660 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" ht="17.6" spans="1:3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="17.6" spans="1:3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="17.6" spans="1:3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="17.6" spans="1:3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" ht="17.6" spans="1:3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="17.6" spans="1:3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="17.6" spans="1:3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="17.6" spans="1:3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="17.6" spans="1:3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="17.6" spans="1:3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="17.6" spans="1:3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" ht="17.6" spans="1:3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="1:4">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" ht="17.6" spans="1:4">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" ht="17.6" spans="1:4">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" ht="17.6" spans="1:8">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" ht="17.6" spans="1:3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" ht="17.6" spans="1:3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="17.6" spans="1:3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" ht="17.6" spans="1:3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" ht="17.6" spans="1:3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" ht="17.6" spans="1:3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" ht="17.6" spans="1:3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" ht="17.6" spans="1:3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" ht="17.6" spans="1:3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" ht="17.6" spans="1:3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1">
+        <v>4</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" ht="17.6" spans="1:3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" ht="17.6" spans="1:3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" ht="17.6" spans="1:3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" ht="17.6" spans="1:3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="17.6" spans="1:3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" ht="17.6" spans="1:3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" ht="17.6" spans="1:3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" ht="17.6" spans="1:3">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" ht="17.6" spans="1:3">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" ht="17.6" spans="1:3">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" ht="17.6" spans="1:3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" ht="17.6" spans="1:3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" ht="17.6" spans="1:3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" ht="17.6" spans="1:3">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" ht="17.6" spans="1:3">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" ht="17.6" spans="1:3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" ht="17.6" spans="1:3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" ht="17.6" spans="1:3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" ht="17.6" spans="1:3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" ht="17.6" spans="1:3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" ht="17.6" spans="1:3">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" ht="17.6" spans="1:3">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" ht="17.6" spans="1:3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" ht="17.6" spans="1:3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" ht="17.6" spans="1:3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" ht="17.6" spans="1:3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" ht="17.6" spans="1:3">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" s="1">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" ht="17.6" spans="1:3">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" ht="17.6" spans="1:3">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" ht="17.6" spans="1:3">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" ht="17.6" spans="1:3">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" s="1">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" ht="17.6" spans="1:3">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1">
+        <v>8</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" ht="17.6" spans="1:3">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1">
+        <v>8</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
